--- a/TestFiles-prod-sanity/PolicyCancellationCarrierAgencyCredit/[MLB]AdvanceStatement-PolicyCancellation-AgencyCredit[Advance].xlsx
+++ b/TestFiles-prod-sanity/PolicyCancellationCarrierAgencyCredit/[MLB]AdvanceStatement-PolicyCancellation-AgencyCredit[Advance].xlsx
@@ -88,7 +88,7 @@
     <t>Integrity Health, LLC</t>
   </si>
   <si>
-    <t>ATENA-ADV-PC-AGC-TEST-X54</t>
+    <t>ATENA-ADV-PC-AGC-TEST-X63</t>
   </si>
   <si>
     <t>ROBERTS, PIPPIN</t>
